--- a/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0003T0006Z000C1N44_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0003T0006Z000C1N44_analysis.xlsx
@@ -480,10 +480,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>101.2212311760144</v>
+        <v>16.44845006610234</v>
       </c>
       <c r="D2" t="n">
-        <v>98.45069205007351</v>
+        <v>15.99823745813695</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
